--- a/LISTAS_ORDENADAS/MI/Fratachos Cinta de perciana Articulos de madera/ZARANDA.xlsx
+++ b/LISTAS_ORDENADAS/MI/Fratachos Cinta de perciana Articulos de madera/ZARANDA.xlsx
@@ -767,14 +767,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="n">
-        <v>45218.52199328757</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="6" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="16">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -796,7 +792,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10" ht="41.25" customHeight="1" s="16">
       <c r="A10" s="17" t="inlineStr">
         <is>
@@ -818,20 +813,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
     <row r="27" ht="64.5" customHeight="1" s="16"/>
     <row r="28" ht="18" customHeight="1" s="16">
       <c r="A28" s="9" t="inlineStr">
@@ -865,7 +846,7 @@
       </c>
       <c r="C29" s="15" t="n"/>
       <c r="D29" s="8" t="n">
-        <v>1001</v>
+        <v>960</v>
       </c>
       <c r="E29" s="3" t="n"/>
     </row>
@@ -880,7 +861,6 @@
       </c>
       <c r="E31" s="3" t="n"/>
     </row>
-    <row r="32"/>
     <row r="33" ht="15.75" customHeight="1" s="16">
       <c r="A33" s="4" t="n"/>
     </row>
@@ -889,12 +869,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="B28:C28"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B29:C29"/>
     <mergeCell ref="A12:D12"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>
